--- a/backend/output/template/模板.xlsx
+++ b/backend/output/template/模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/Krun/backend/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF11C341-AA07-F949-BD48-67599EDD161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1D5BA8-DFBF-6142-9285-8FCD11913B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="48200" yWindow="7360" windowWidth="28580" windowHeight="17440" xr2:uid="{B4CDD553-F6E2-E74E-A789-E7CE3B2875FD}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>场景1名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,77 +69,132 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value2</t>
+  </si>
+  <si>
+    <t>value3</t>
+  </si>
+  <si>
+    <t>v1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>age</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>city</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>xpath.field3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value2</t>
-  </si>
-  <si>
-    <t>value3</t>
-  </si>
-  <si>
-    <t>v1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xpath.field4</t>
+  </si>
+  <si>
+    <t>xpath.field5</t>
+  </si>
+  <si>
+    <t>value4</t>
+  </si>
+  <si>
+    <t>value5</t>
+  </si>
+  <si>
+    <t>v3</t>
+  </si>
+  <si>
+    <t>v4</t>
+  </si>
+  <si>
+    <t>v5</t>
+  </si>
+  <si>
+    <t>场景4名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>val1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>val2</t>
+  </si>
+  <si>
+    <t>val3</t>
+  </si>
+  <si>
+    <t>val4</t>
+  </si>
+  <si>
+    <t>val5</t>
+  </si>
+  <si>
+    <t>va1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>va2</t>
+  </si>
+  <si>
+    <t>va3</t>
+  </si>
+  <si>
+    <t>va4</t>
+  </si>
+  <si>
+    <t>va5</t>
   </si>
   <si>
     <t>v2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>里斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>age</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>city</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上海</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>北京</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广州</t>
+  </si>
+  <si>
+    <t>$.user.workno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -205,7 +260,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,6 +268,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -529,10 +587,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C401589C-A87D-0D49-B83B-478A1235A391}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -543,126 +601,213 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B10" s="1">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1">
-        <v>19</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="E11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4224</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1234</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
